--- a/Rubricas_6ago2025.xlsx
+++ b/Rubricas_6ago2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ageidv/ilo/deploy_3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBCF9D26-4B75-A040-A02B-CB75340EA718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0EDB6D9-EC73-354E-866E-A06FD02F6E51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="800" windowWidth="26020" windowHeight="16880" tabRatio="500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3106,14 +3106,14 @@
     <t>alto: políticas del mercado laboral diseñadas para asegurar empleos sostenibles y resiliencia económica-ambiental a largo plazo.</t>
   </si>
   <si>
-    <t>2.5. Asegurar una estructura organizacional con perspectiva de género (recursos financieros).</t>
+    <t>2.5 Asegurar una estructura organizacional y presupuestal con perspectiva de genero</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3283,6 +3283,13 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -3350,7 +3357,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3458,6 +3465,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4791,7 +4799,7 @@
       </c>
       <c r="H2" s="12"/>
     </row>
-    <row r="3" spans="1:8" ht="262" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="240" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
         <v>163</v>
       </c>
@@ -4815,7 +4823,7 @@
       </c>
       <c r="H3" s="12"/>
     </row>
-    <row r="4" spans="1:8" ht="168" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="156" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
         <v>168</v>
       </c>
@@ -4839,7 +4847,7 @@
       </c>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:8" ht="144" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="132" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
         <v>173</v>
       </c>
@@ -4863,7 +4871,7 @@
       </c>
       <c r="H5" s="12"/>
     </row>
-    <row r="6" spans="1:8" ht="120" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="108" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
         <v>178</v>
       </c>
@@ -4935,7 +4943,7 @@
       </c>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:8" ht="228" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="216" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>193</v>
       </c>
@@ -4982,10 +4990,10 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="120" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="39" t="s">
         <v>927</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="39" t="s">
         <v>927</v>
       </c>
       <c r="C11" s="16" t="s">
@@ -5050,7 +5058,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="108" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
         <v>217</v>
       </c>
@@ -5096,7 +5104,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="72" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="60" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
         <v>227</v>
       </c>
@@ -5119,7 +5127,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" ht="84" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>232</v>
       </c>
@@ -5142,7 +5150,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="144" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" ht="132" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>237</v>
       </c>
@@ -5211,7 +5219,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="156" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" ht="144" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>252</v>
       </c>
@@ -5528,7 +5536,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="91" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:7" ht="104" x14ac:dyDescent="0.2">
       <c r="B17" s="20" t="s">
         <v>82</v>
       </c>
@@ -5553,7 +5561,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="118" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:7" ht="131" x14ac:dyDescent="0.2">
       <c r="B19" s="18" t="s">
         <v>265</v>
       </c>
@@ -5834,7 +5842,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="128" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="144" x14ac:dyDescent="0.2">
       <c r="A8" s="27" t="s">
         <v>272</v>
       </c>
@@ -6813,7 +6821,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="102" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" ht="85" x14ac:dyDescent="0.2">
       <c r="A25" s="32" t="s">
         <v>543</v>
       </c>
@@ -6893,7 +6901,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A29" s="32" t="s">
         <v>543</v>
       </c>
@@ -7013,7 +7021,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="102" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" ht="85" x14ac:dyDescent="0.2">
       <c r="A35" s="36" t="s">
         <v>594</v>
       </c>
@@ -7153,7 +7161,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="102" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" ht="85" x14ac:dyDescent="0.2">
       <c r="A42" s="32" t="s">
         <v>645</v>
       </c>
@@ -7532,7 +7540,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="85" x14ac:dyDescent="0.2">
       <c r="A11" s="32" t="s">
         <v>441</v>
       </c>
@@ -7592,7 +7600,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="85" x14ac:dyDescent="0.2">
       <c r="A14" s="32" t="s">
         <v>492</v>
       </c>
@@ -7632,7 +7640,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="85" x14ac:dyDescent="0.2">
       <c r="A16" s="32" t="s">
         <v>492</v>
       </c>
@@ -7652,7 +7660,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="85" x14ac:dyDescent="0.2">
       <c r="A17" s="32" t="s">
         <v>492</v>
       </c>
